--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6805.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6805.xlsx
@@ -1854,6 +1854,9 @@
       <c r="F21" t="n">
         <v>0.172</v>
       </c>
+      <c r="G21" t="n">
+        <v>0.33</v>
+      </c>
       <c r="H21" t="n">
         <v>0.4375</v>
       </c>
@@ -1875,12 +1878,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-04-02-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-04-02-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-04-02-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-04-02-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-04-02-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-04-02-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1911,6 +1914,9 @@
       <c r="F22" t="n">
         <v>0.172</v>
       </c>
+      <c r="G22" t="n">
+        <v>0.43</v>
+      </c>
       <c r="H22" t="n">
         <v>0.4375</v>
       </c>
@@ -1932,12 +1938,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-04-04-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-04-04-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-04-04-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-04-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-04-04-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-04-04-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1968,6 +1974,9 @@
       <c r="F23" t="n">
         <v>0.297</v>
       </c>
+      <c r="G23" t="n">
+        <v>0.57</v>
+      </c>
       <c r="H23" t="n">
         <v>0.5625</v>
       </c>
@@ -1989,12 +1998,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-06-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-06-06-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-06-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-06-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-06-06-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-06-06-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2025,6 +2034,9 @@
       <c r="F24" t="n">
         <v>0.391</v>
       </c>
+      <c r="G24" t="n">
+        <v>0.7</v>
+      </c>
       <c r="H24" t="n">
         <v>0.75</v>
       </c>
@@ -2046,12 +2058,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-08-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-08-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-08-08-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-08-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-08-08-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-08-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2082,6 +2094,9 @@
       <c r="F25" t="n">
         <v>0.484</v>
       </c>
+      <c r="G25" t="n">
+        <v>0.7</v>
+      </c>
       <c r="H25" t="n">
         <v>0.875</v>
       </c>
@@ -2103,12 +2118,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-10-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-10-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-10-08-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-10-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-10-08-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-10-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2139,6 +2154,9 @@
       <c r="F26" t="n">
         <v>0.609</v>
       </c>
+      <c r="G26" t="n">
+        <v>0.7</v>
+      </c>
       <c r="H26" t="n">
         <v>1.0625</v>
       </c>
@@ -2160,12 +2178,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-12-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-12-08-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-12-08-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-12-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-12-08-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-12-08-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2196,6 +2214,9 @@
       <c r="F27" t="n">
         <v>0.844</v>
       </c>
+      <c r="G27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="H27" t="n">
         <v>1.3125</v>
       </c>
@@ -2217,12 +2238,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-16-12-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-16-12-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-16-12-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-16-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-16-12-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-16-12-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2253,6 +2274,9 @@
       <c r="F28" t="n">
         <v>0.844</v>
       </c>
+      <c r="G28" t="n">
+        <v>1.14</v>
+      </c>
       <c r="H28" t="n">
         <v>1.3125</v>
       </c>
@@ -2274,12 +2298,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-16-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-16-16-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-16-16-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-16-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-16-16-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-16-16-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2310,6 +2334,9 @@
       <c r="F29" t="n">
         <v>1.078</v>
       </c>
+      <c r="G29" t="n">
+        <v>1.48</v>
+      </c>
       <c r="H29" t="n">
         <v>1.625</v>
       </c>
@@ -2331,12 +2358,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-20-20-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: C4HEX@HEX, D@BORE, ORB_GRVDIA@DRIVE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6805-20-20-NWO (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-20-20-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-20-20-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6805-20-20-NWO dims are NOT assumed; confirm before modelling | Brennan CAD record 6805-20-20-NWO-FG (PARTcommunity / CADENAS, C4HEX@HEX=C, D@BORE=BD, ORB_GRVDIA@DRIVE=HL, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
